--- a/Data masking.xlsx
+++ b/Data masking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SteffenRasmussen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E669DA84-0240-4018-A7D6-9E6A8C1C299F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90053DB9-2CFF-4580-B168-0398DE07E13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{218DA12B-913B-4493-9591-C474226A67AE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="37">
   <si>
     <t>Ejer</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Udgifter</t>
+  </si>
+  <si>
+    <t>ny test</t>
   </si>
 </sst>
 </file>
@@ -522,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15F1F404-9886-4DB2-805F-623307011384}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -572,15 +575,15 @@
       </c>
       <c r="E2" s="1">
         <f ca="1">RANDBETWEEN(500000,1000000)</f>
-        <v>875815</v>
+        <v>508884</v>
       </c>
       <c r="F2" s="1">
         <f ca="1">RANDBETWEEN(500000,1000000)</f>
-        <v>747532</v>
+        <v>543207</v>
       </c>
       <c r="G2" s="1">
         <f ca="1">RANDBETWEEN(100000,200000)</f>
-        <v>116586</v>
+        <v>114021</v>
       </c>
       <c r="H2">
         <v>15</v>
@@ -601,15 +604,15 @@
       </c>
       <c r="E3" s="1">
         <f t="shared" ref="E3:F21" ca="1" si="0">RANDBETWEEN(500000,1000000)</f>
-        <v>911871</v>
+        <v>952466</v>
       </c>
       <c r="F3" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>958488</v>
+        <v>779003</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" ref="G3:G26" ca="1" si="1">RANDBETWEEN(100000,200000)</f>
-        <v>134747</v>
+        <v>132340</v>
       </c>
       <c r="H3">
         <v>15</v>
@@ -630,15 +633,15 @@
       </c>
       <c r="E4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>550122</v>
+        <v>692931</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>787237</v>
+        <v>808873</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>130484</v>
+        <v>117063</v>
       </c>
       <c r="H4">
         <v>15</v>
@@ -659,15 +662,15 @@
       </c>
       <c r="E5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>924012</v>
+        <v>738054</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>554566</v>
+        <v>571424</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>190958</v>
+        <v>174387</v>
       </c>
       <c r="H5">
         <v>17</v>
@@ -688,15 +691,15 @@
       </c>
       <c r="E6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>617051</v>
+        <v>585168</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>994411</v>
+        <v>914767</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>197044</v>
+        <v>157082</v>
       </c>
       <c r="H6">
         <v>17</v>
@@ -717,15 +720,15 @@
       </c>
       <c r="E7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>740996</v>
+        <v>590151</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>786044</v>
+        <v>979723</v>
       </c>
       <c r="G7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>190137</v>
+        <v>149582</v>
       </c>
       <c r="H7">
         <v>16</v>
@@ -746,15 +749,15 @@
       </c>
       <c r="E8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>758805</v>
+        <v>912607</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>552249</v>
+        <v>878145</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>156129</v>
+        <v>193979</v>
       </c>
       <c r="H8">
         <v>16</v>
@@ -775,15 +778,15 @@
       </c>
       <c r="E9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>816440</v>
+        <v>653229</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>831328</v>
+        <v>616294</v>
       </c>
       <c r="G9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>154454</v>
+        <v>126311</v>
       </c>
       <c r="H9">
         <v>15</v>
@@ -804,15 +807,15 @@
       </c>
       <c r="E10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>971419</v>
+        <v>608309</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>916323</v>
+        <v>834588</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>186965</v>
+        <v>135206</v>
       </c>
       <c r="H10">
         <v>15</v>
@@ -833,15 +836,15 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>956820</v>
+        <v>730736</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>988349</v>
+        <v>542687</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>145399</v>
+        <v>183315</v>
       </c>
       <c r="H11">
         <v>14</v>
@@ -862,15 +865,15 @@
       </c>
       <c r="E12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>542100</v>
+        <v>791571</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>749871</v>
+        <v>543554</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>135122</v>
+        <v>104326</v>
       </c>
       <c r="H12">
         <v>14</v>
@@ -891,15 +894,15 @@
       </c>
       <c r="E13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>613082</v>
+        <v>554216</v>
       </c>
       <c r="F13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>909593</v>
+        <v>710732</v>
       </c>
       <c r="G13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>168117</v>
+        <v>154786</v>
       </c>
       <c r="H13">
         <v>13</v>
@@ -920,15 +923,15 @@
       </c>
       <c r="E14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>906976</v>
+        <v>830594</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>952703</v>
+        <v>515891</v>
       </c>
       <c r="G14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>117096</v>
+        <v>153400</v>
       </c>
       <c r="H14">
         <v>13</v>
@@ -949,15 +952,15 @@
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>581808</v>
+        <v>970617</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>746637</v>
+        <v>681980</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>161929</v>
+        <v>196791</v>
       </c>
       <c r="H15">
         <v>12</v>
@@ -978,15 +981,15 @@
       </c>
       <c r="E16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>611040</v>
+        <v>561763</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>840496</v>
+        <v>584988</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>110071</v>
+        <v>190099</v>
       </c>
       <c r="H16">
         <v>12</v>
@@ -1007,15 +1010,15 @@
       </c>
       <c r="E17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>744600</v>
+        <v>755379</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>677424</v>
+        <v>987936</v>
       </c>
       <c r="G17" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>162613</v>
+        <v>101360</v>
       </c>
       <c r="H17">
         <v>11</v>
@@ -1036,15 +1039,15 @@
       </c>
       <c r="E18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>734119</v>
+        <v>630039</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>921508</v>
+        <v>974385</v>
       </c>
       <c r="G18" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>187579</v>
+        <v>153509</v>
       </c>
       <c r="H18">
         <v>11</v>
@@ -1065,15 +1068,15 @@
       </c>
       <c r="E19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>799763</v>
+        <v>581224</v>
       </c>
       <c r="F19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>848128</v>
+        <v>690356</v>
       </c>
       <c r="G19" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>145941</v>
+        <v>104792</v>
       </c>
       <c r="H19">
         <v>10</v>
@@ -1094,15 +1097,15 @@
       </c>
       <c r="E20" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>716553</v>
+        <v>856258</v>
       </c>
       <c r="F20" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>524840</v>
+        <v>516481</v>
       </c>
       <c r="G20" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>187347</v>
+        <v>171721</v>
       </c>
       <c r="H20">
         <v>10</v>
@@ -1123,15 +1126,15 @@
       </c>
       <c r="E21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>854250</v>
+        <v>985060</v>
       </c>
       <c r="F21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>503077</v>
+        <v>811599</v>
       </c>
       <c r="G21" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>169725</v>
+        <v>188817</v>
       </c>
       <c r="H21">
         <v>18</v>
@@ -1152,15 +1155,15 @@
       </c>
       <c r="E22" s="1">
         <f t="shared" ref="E22:F26" ca="1" si="2">RANDBETWEEN(500000,1000000)</f>
-        <v>597502</v>
+        <v>802193</v>
       </c>
       <c r="F22" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>554481</v>
+        <v>764778</v>
       </c>
       <c r="G22" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>189620</v>
+        <v>100863</v>
       </c>
       <c r="H22">
         <v>18</v>
@@ -1181,15 +1184,15 @@
       </c>
       <c r="E23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>930814</v>
+        <v>652300</v>
       </c>
       <c r="F23" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>558720</v>
+        <v>992015</v>
       </c>
       <c r="G23" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>110907</v>
+        <v>187459</v>
       </c>
       <c r="H23">
         <v>19</v>
@@ -1210,15 +1213,15 @@
       </c>
       <c r="E24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>921806</v>
+        <v>722372</v>
       </c>
       <c r="F24" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>746824</v>
+        <v>942285</v>
       </c>
       <c r="G24" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>161359</v>
+        <v>191167</v>
       </c>
       <c r="H24">
         <v>19</v>
@@ -1239,15 +1242,15 @@
       </c>
       <c r="E25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>535335</v>
+        <v>934874</v>
       </c>
       <c r="F25" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>890599</v>
+        <v>855136</v>
       </c>
       <c r="G25" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>117330</v>
+        <v>184451</v>
       </c>
       <c r="H25">
         <v>20</v>
@@ -1268,18 +1271,38 @@
       </c>
       <c r="E26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>834694</v>
+        <v>561524</v>
       </c>
       <c r="F26" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>502326</v>
+        <v>697839</v>
       </c>
       <c r="G26" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>110863</v>
+        <v>193016</v>
       </c>
       <c r="H26">
         <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
